--- a/reports/MenuRadar_2026-06-08.xlsx
+++ b/reports/MenuRadar_2026-06-08.xlsx
@@ -7,10 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="خلاصه کل" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="روماتای" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="برگر فکتوری" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="لفو" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="روماتای" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="برگر فکتوری" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="لفو" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,12 +42,6 @@
     <font>
       <name val="Arial"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
     </font>
   </fonts>
   <fills count="6">
@@ -105,9 +98,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -118,9 +111,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -487,1846 +477,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>📋 خلاصه مقایسه قیمت — همه کانسپت‌ها</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>کانسپت</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>آیتم من</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>قیمت من (تومان)</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>آیتم رقیب</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>قیمت رقیب (تومان)</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>رقیب</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>اختلاف (تومان)</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>وضعیت</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>روماتای</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>پانینی اسفناج</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>258500</v>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>BOP باپ t BOP برنج داغ به همراه سس مخصوص باپ اسفناج پنیر پارمیزان t</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>145500</v>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>113000</v>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>🔴 گران‌تر</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>روماتای</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>نودل سوپ مرغ</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>786500</v>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Pad Thai Noodles chicken چیکن نودل برنج تخم مرغ میکس سبزیجات سس ترش و شیرین t</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>151200</v>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>635300</v>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>🔴 گران‌تر</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>روماتای</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>نان سیر</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>435600</v>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Asian Chopped Chicken مرغ گریل شده کلم سفید کلم قرمز گشنیز نان کریسپی سس کنجد t</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>904000</v>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>-468400</v>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>🟢 ارزان‌تر</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>روماتای</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>نودل سرخ شده با مرغ سبزیجات</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>871200</v>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Chicken Noodles مرغ مزه دار شده میکس سبزیجات سس سیشوان t</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>124500</v>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>746700</v>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>🔴 گران‌تر</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>روماتای</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>نودل سرخ شده با میگوسبزیجات</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>1452000</v>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Nakaya Maki میگو سرخ شده سوریمی کاتسو آووکادو توبیکو سبز سلمن t</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>214300</v>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>1237700</v>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>🔴 گران‌تر</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>روماتای</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">برنج سرخ شده با مرغ سبزیجات </t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>665500</v>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Chicken Teryaki مرغ گریل شده در سس تریاکی برنج بخارپز سبزیجات گریل شده t</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>107000</v>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>558500</v>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>🔴 گران‌تر</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>روماتای</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>برنج سرخ شده با گوشت سبزیجات</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>1089000</v>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Beef Teryaki گوشت گریل شده در سس تریاکی برنج بخارپز سبزیجات گریل شده t</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>206000</v>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>883000</v>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>🔴 گران‌تر</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>روماتای</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>برنج سرخ شده با میگو سبزیجات</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>1306800</v>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Shrimp Teryaki میگو گریل شده در سس تریاکی برنج بخارپز سبزیجات گریل شده t</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>278000</v>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>1028800</v>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>🔴 گران‌تر</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>روماتای</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>بیف تریاكی</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>1089000</v>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Beef Noodles بیف به همراه فلفل سیاه فلفل رنگی پیازچه t</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>171200</v>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>917800</v>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>🔴 گران‌تر</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>روماتای</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>مرغ کانتون</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>711700</v>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>Korean Fried Chicken مرغ سوخاری سس چیلی کُره ای و خیارشور t</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>693000</v>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>18700</v>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>🔴 گران‌تر</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>روماتای</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>میگو سوخاری</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>1210000</v>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>Crispy Maki Roll میگو کاتسو آووکادو خیار مایونز ژاپنی t</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>125900</v>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>1084100</v>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>🔴 گران‌تر</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>روماتای</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> پاستا سبزیجات</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>653400</v>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Vegetable Noodles نودل میکس سبزیجات سس سیشوان t</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>107000</v>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>546400</v>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>🔴 گران‌تر</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>روماتای</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>سیب زمینی سرخ شده روماتای</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>255200</v>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Nakaya Maki میگو سرخ شده سوریمی کاتسو آووکادو توبیکو سبز سلمن t</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>214300</v>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>40900</v>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>🔴 گران‌تر</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>روماتای</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>برنج بخارپز</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>254100</v>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Steam Rice برنج بخارپز t Steam Rice t</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>315000</v>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>-60900</v>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>🟢 ارزان‌تر</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>روماتای</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>بیف استراگانف</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>1149500</v>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>Beef Noodles بیف به همراه فلفل سیاه فلفل رنگی پیازچه t</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>171200</v>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>978300</v>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>🔴 گران‌تر</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>روماتای</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>فیله مرغ</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>181500</v>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>Korean Fried Chicken مرغ سوخاری سس چیلی کُره ای و خیارشور t</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>693000</v>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>-511500</v>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>🟢 ارزان‌تر</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>روماتای</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>روکولا</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="n">
-        <v>133100</v>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>Beef Sliders بیف قارچ واسابی خامه ای چدار روکولا سس هالوپینو t</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>627000</v>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>-493900</v>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>🟢 ارزان‌تر</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>روماتای</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>قارچ روماتای</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>271700</v>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>Miso Mashroom توفو جلبک دریایی پیازچه مخلوط قارچ t</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>482000</v>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>-210300</v>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>🟢 ارزان‌تر</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>روماتای</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>پنیر پیتزا</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="n">
-        <v>41000</v>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>Crazy Mushroom Maki قارچ تمپپرا پنیر آووکادو خیار سس پونزو t</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>156900</v>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>-115900</v>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>🟢 ارزان‌تر</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>روماتای</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>چیكن ماشروم</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>750200</v>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>Miso Mashroom میسو ماشروم t Miso Mashroom توفو جلبک دریایی پیازچه مخلوط قارچ t</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>482000</v>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>268200</v>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>🔴 گران‌تر</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>روماتای</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>شنیسل مرغ با سس قارچ</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="n">
-        <v>750200</v>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>Tamari Fried Ch مرغ میکس سبزیجات تخم مرغ قارچ سس تاماری t</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>796000</v>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>-45800</v>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>🟢 ارزان‌تر</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>روماتای</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>چیکن استراگانف</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>695200</v>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>Korean Fried Chicken مرغ سوخاری سس چیلی کُره ای و خیارشور t</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>693000</v>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>2200</v>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>🟡 مشابه</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>روماتای</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>میکس برنج و نودل سرخ شده</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="n">
-        <v>592900</v>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>Pad Thai Noodles chicken چیکن نودل برنج تخم مرغ میکس سبزیجات سس ترش و شیرین t</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>151200</v>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>441700</v>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>🔴 گران‌تر</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>روماتای</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>سس سبز</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>49500</v>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>Salmon oshi sushi سلمن آووکادو سس چیلی گارلیک فلفل سبز t</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>206800</v>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="n">
-        <v>-157300</v>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>🟢 ارزان‌تر</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>روماتای</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>سیب زمینی با سس قارچ روماتای</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="n">
-        <v>388300</v>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>Mashrooms and Veggie Cigar میکس سه نوع قارچ سس ورچستر t</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>598000</v>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>-209700</v>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>🟢 ارزان‌تر</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>روماتای</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>چیکن فونگی</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>786500</v>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>Korean Fried Chicken مرغ سوخاری سس چیلی کُره ای و خیارشور t</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>693000</v>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="n">
-        <v>93500</v>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>🔴 گران‌تر</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>روماتای</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پیتزا استیک </t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="n">
-        <v>1149500</v>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>Nakaya Panko Steak استیک تندرلوین سوخاری شده سس قارچ خامه ای سالاد کرانچی t</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>166500</v>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>983000</v>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>🔴 گران‌تر</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>روماتای</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>لازانیا کلاسیک</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>792000</v>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>Classic Mojito کلاسیک موهیتو t Classic Mojito t</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>356000</v>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="n">
-        <v>436000</v>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>🔴 گران‌تر</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>روماتای</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>چیکن فلورنتینو</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="n">
-        <v>980100</v>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>Korean Fried Chicken مرغ سوخاری سس چیلی کُره ای و خیارشور t</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>693000</v>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>287100</v>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>🔴 گران‌تر</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>روماتای</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>مرغ ترش و شیرین</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="n">
-        <v>883300</v>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>Pad Thai Noodles chicken چیکن نودل برنج تخم مرغ میکس سبزیجات سس ترش و شیرین t</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>151200</v>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="n">
-        <v>732100</v>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>🔴 گران‌تر</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>روماتای</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">بال مرغ </t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="n">
-        <v>352000</v>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>Korean Fried Chicken مرغ سوخاری سس چیلی کُره ای و خیارشور t</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>693000</v>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>-341000</v>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>🟢 ارزان‌تر</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>روماتای</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>رول مرغ و قارچ</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="n">
-        <v>330000</v>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>Korean Fried Chicken مرغ سوخاری سس چیلی کُره ای و خیارشور t</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>693000</v>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="n">
-        <v>-363000</v>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>🟢 ارزان‌تر</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>روماتای</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>رول سبزیجات</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="n">
-        <v>295900</v>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>Vegetable Noodles نودل میکس سبزیجات سس سیشوان t</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>107000</v>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="n">
-        <v>188900</v>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>🔴 گران‌تر</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>روماتای</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>رول مرغ و قارچ عددی</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="n">
-        <v>115500</v>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>Korean Fried Chicken مرغ سوخاری سس چیلی کُره ای و خیارشور t</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="n">
-        <v>693000</v>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G36" s="4" t="n">
-        <v>-577500</v>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>🟢 ارزان‌تر</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>روماتای</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>برنج بخارپز ساید</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="n">
-        <v>169400</v>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>Steam Rice برنج بخارپز t Steam Rice t</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>315000</v>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>-145600</v>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>🟢 ارزان‌تر</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>روماتای</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>برنج سرخ شده سبزیجات ساید</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="n">
-        <v>290400</v>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>Chicken Teryaki مرغ گریل شده در سس تریاکی برنج بخارپز سبزیجات گریل شده t</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>107000</v>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G38" s="4" t="n">
-        <v>183400</v>
-      </c>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>🔴 گران‌تر</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>روماتای</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>نودل سرخ شده سبزیجات ساید</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="n">
-        <v>556600</v>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>Vegetable Noodles نودل میکس سبزیجات سس سیشوان t</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>107000</v>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>449600</v>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>🔴 گران‌تر</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>روماتای</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>راک شریمپ</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="n">
-        <v>646800</v>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>Rock &amp; Roll سوریمی خیار مامی نوری میگو راک t</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="n">
-        <v>235700</v>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="n">
-        <v>411100</v>
-      </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>🔴 گران‌تر</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>روماتای</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>تریاکی چیکن</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="n">
-        <v>828300</v>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>Chicken Teryaki مرغ گریل شده در سس تریاکی برنج بخارپز سبزیجات گریل شده t</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>107000</v>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>721300</v>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>🔴 گران‌تر</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>روماتای</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>چیکن سامبال</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="n">
-        <v>713900</v>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>Korean Fried Chicken مرغ سوخاری سس چیلی کُره ای و خیارشور t</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>693000</v>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G42" s="4" t="n">
-        <v>20900</v>
-      </c>
-      <c r="H42" s="4" t="inlineStr">
-        <is>
-          <t>🔴 گران‌تر</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>روماتای</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>نودل با سبزیجات</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="n">
-        <v>755700</v>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>Vegetable Noodles نودل میکس سبزیجات سس سیشوان t</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>107000</v>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>648700</v>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>🔴 گران‌تر</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>روماتای</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>برنج با سبزیجات</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="n">
-        <v>556600</v>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>Chicken Teryaki مرغ گریل شده در سس تریاکی برنج بخارپز سبزیجات گریل شده t</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="n">
-        <v>107000</v>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G44" s="4" t="n">
-        <v>449600</v>
-      </c>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>🔴 گران‌تر</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>روماتای</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>بیف بیزیل</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="n">
-        <v>1210000</v>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>Beef Noodles بیف به همراه فلفل سیاه فلفل رنگی پیازچه t</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>171200</v>
-      </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="n">
-        <v>1038800</v>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>🔴 گران‌تر</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>روماتای</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>استیک پراوانس</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="n">
-        <v>1113200</v>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>Nakaya Panko Steak استیک تندرلوین سوخاری شده سس قارچ خامه ای سالاد کرانچی t</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="n">
-        <v>166500</v>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G46" s="4" t="n">
-        <v>946700</v>
-      </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>🔴 گران‌تر</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>روماتای</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>کالزونه مرغ و اسفناج</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="n">
-        <v>578600</v>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>Korean Fried Chicken مرغ سوخاری سس چیلی کُره ای و خیارشور t</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="n">
-        <v>693000</v>
-      </c>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="n">
-        <v>-114400</v>
-      </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>🟢 ارزان‌تر</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>روماتای</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>لیموناد قوطی</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="n">
-        <v>70000</v>
-      </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>Lemonade لیموناد t Lemonade t</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="n">
-        <v>316000</v>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G48" s="4" t="n">
-        <v>-246000</v>
-      </c>
-      <c r="H48" s="4" t="inlineStr">
-        <is>
-          <t>🟢 ارزان‌تر</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>روماتای</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>موهیتو قوطی</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="n">
-        <v>80000</v>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>Classic Mojito کلاسیک موهیتو t Classic Mojito t</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="n">
-        <v>356000</v>
-      </c>
-      <c r="F49" s="3" t="inlineStr">
-        <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G49" s="3" t="n">
-        <v>-276000</v>
-      </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>🟢 ارزان‌تر</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>روماتای</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>فیله مرغ سوخاری عددی</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="n">
-        <v>143000</v>
-      </c>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>Korean Fried Chicken مرغ سوخاری سس چیلی کُره ای و خیارشور t</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="n">
-        <v>693000</v>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G50" s="4" t="n">
-        <v>-550000</v>
-      </c>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>🟢 ارزان‌تر</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>روماتای</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>میگو سوخاری عددی</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="n">
-        <v>176000</v>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>Crispy Maki Roll میگو کاتسو آووکادو خیار مایونز ژاپنی t</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="n">
-        <v>125900</v>
-      </c>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G51" s="3" t="n">
-        <v>50100</v>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>🔴 گران‌تر</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:H95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2341,7 +491,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>📊 مقایسه منو — روماتای  |  تعداد رقبا: 9</t>
         </is>
@@ -2405,23 +555,27 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>BOP باپ t BOP برنج داغ به همراه سس مخصوص باپ اسفناج پنیر پارمیزان t</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>145500</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>113000</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>🔴 گران‌تر</t>
+          <t>⚪ بدون تطابق</t>
         </is>
       </c>
     </row>
@@ -2521,23 +675,27 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Pad Thai Noodles chicken چیکن نودل برنج تخم مرغ میکس سبزیجات سس ترش و شیرین t</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>151200</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>635300</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>🔴 گران‌تر</t>
+          <t>⚪ بدون تطابق</t>
         </is>
       </c>
     </row>
@@ -2597,23 +755,27 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Asian Chopped Chicken مرغ گریل شده کلم سفید کلم قرمز گشنیز نان کریسپی سس کنجد t</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>904000</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>-468400</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>🟢 ارزان‌تر</t>
+          <t>⚪ بدون تطابق</t>
         </is>
       </c>
     </row>
@@ -2713,23 +875,27 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Chicken Noodles مرغ مزه دار شده میکس سبزیجات سس سیشوان t</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>124500</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>746700</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>🔴 گران‌تر</t>
+          <t>⚪ بدون تطابق</t>
         </is>
       </c>
     </row>
@@ -2789,23 +955,27 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Nakaya Maki میگو سرخ شده سوریمی کاتسو آووکادو توبیکو سبز سلمن t</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>214300</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>1237700</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>🔴 گران‌تر</t>
+          <t>⚪ بدون تطابق</t>
         </is>
       </c>
     </row>
@@ -2825,23 +995,27 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Chicken Teryaki مرغ گریل شده در سس تریاکی برنج بخارپز سبزیجات گریل شده t</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>107000</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>558500</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>🔴 گران‌تر</t>
+          <t>⚪ بدون تطابق</t>
         </is>
       </c>
     </row>
@@ -2861,23 +1035,27 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Beef Teryaki گوشت گریل شده در سس تریاکی برنج بخارپز سبزیجات گریل شده t</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>206000</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>883000</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>🔴 گران‌تر</t>
+          <t>⚪ بدون تطابق</t>
         </is>
       </c>
     </row>
@@ -2897,23 +1075,27 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Shrimp Teryaki میگو گریل شده در سس تریاکی برنج بخارپز سبزیجات گریل شده t</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>278000</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>1028800</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>🔴 گران‌تر</t>
+          <t>⚪ بدون تطابق</t>
         </is>
       </c>
     </row>
@@ -2933,23 +1115,27 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Beef Noodles بیف به همراه فلفل سیاه فلفل رنگی پیازچه t</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>171200</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>917800</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>🔴 گران‌تر</t>
+          <t>⚪ بدون تطابق</t>
         </is>
       </c>
     </row>
@@ -3009,23 +1195,27 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Korean Fried Chicken مرغ سوخاری سس چیلی کُره ای و خیارشور t</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>693000</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>18700</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>🔴 گران‌تر</t>
+          <t>⚪ بدون تطابق</t>
         </is>
       </c>
     </row>
@@ -3045,23 +1235,27 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Crispy Maki Roll میگو کاتسو آووکادو خیار مایونز ژاپنی t</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>125900</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>1084100</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>🔴 گران‌تر</t>
+          <t>⚪ بدون تطابق</t>
         </is>
       </c>
     </row>
@@ -3081,23 +1275,27 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Vegetable Noodles نودل میکس سبزیجات سس سیشوان t</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>107000</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>546400</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>🔴 گران‌تر</t>
+          <t>⚪ بدون تطابق</t>
         </is>
       </c>
     </row>
@@ -3477,23 +1675,27 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Nakaya Maki میگو سرخ شده سوریمی کاتسو آووکادو توبیکو سبز سلمن t</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>214300</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>40900</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>🔴 گران‌تر</t>
+          <t>⚪ بدون تطابق</t>
         </is>
       </c>
     </row>
@@ -3513,23 +1715,27 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Steam Rice برنج بخارپز t Steam Rice t</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>315000</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="n">
-        <v>-60900</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>🟢 ارزان‌تر</t>
+          <t>⚪ بدون تطابق</t>
         </is>
       </c>
     </row>
@@ -3549,23 +1755,27 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Beef Noodles بیف به همراه فلفل سیاه فلفل رنگی پیازچه t</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>171200</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>978300</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>🔴 گران‌تر</t>
+          <t>⚪ بدون تطابق</t>
         </is>
       </c>
     </row>
@@ -3625,23 +1835,27 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Korean Fried Chicken مرغ سوخاری سس چیلی کُره ای و خیارشور t</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>693000</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="n">
-        <v>-511500</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>🟢 ارزان‌تر</t>
+          <t>⚪ بدون تطابق</t>
         </is>
       </c>
     </row>
@@ -3661,23 +1875,27 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Beef Sliders بیف قارچ واسابی خامه ای چدار روکولا سس هالوپینو t</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="n">
-        <v>627000</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G36" s="4" t="n">
-        <v>-493900</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>🟢 ارزان‌تر</t>
+          <t>⚪ بدون تطابق</t>
         </is>
       </c>
     </row>
@@ -3697,23 +1915,27 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Miso Mashroom توفو جلبک دریایی پیازچه مخلوط قارچ t</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>482000</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>-210300</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>🟢 ارزان‌تر</t>
+          <t>⚪ بدون تطابق</t>
         </is>
       </c>
     </row>
@@ -3773,23 +1995,27 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Crazy Mushroom Maki قارچ تمپپرا پنیر آووکادو خیار سس پونزو t</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>156900</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>-115900</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>🟢 ارزان‌تر</t>
+          <t>⚪ بدون تطابق</t>
         </is>
       </c>
     </row>
@@ -3849,23 +2075,27 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Miso Mashroom میسو ماشروم t Miso Mashroom توفو جلبک دریایی پیازچه مخلوط قارچ t</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>482000</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>268200</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>🔴 گران‌تر</t>
+          <t>⚪ بدون تطابق</t>
         </is>
       </c>
     </row>
@@ -3885,23 +2115,27 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Tamari Fried Ch مرغ میکس سبزیجات تخم مرغ قارچ سس تاماری t</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>796000</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G42" s="4" t="n">
-        <v>-45800</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>🟢 ارزان‌تر</t>
+          <t>⚪ بدون تطابق</t>
         </is>
       </c>
     </row>
@@ -4001,23 +2235,27 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Korean Fried Chicken مرغ سوخاری سس چیلی کُره ای و خیارشور t</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>693000</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="n">
-        <v>2200</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>🟡 مشابه</t>
+          <t>⚪ بدون تطابق</t>
         </is>
       </c>
     </row>
@@ -4077,23 +2315,27 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Pad Thai Noodles chicken چیکن نودل برنج تخم مرغ میکس سبزیجات سس ترش و شیرین t</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="n">
-        <v>151200</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="n">
-        <v>441700</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>🔴 گران‌تر</t>
+          <t>⚪ بدون تطابق</t>
         </is>
       </c>
     </row>
@@ -4153,23 +2395,27 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Salmon oshi sushi سلمن آووکادو سس چیلی گارلیک فلفل سبز t</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="n">
-        <v>206800</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G49" s="3" t="n">
-        <v>-157300</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>🟢 ارزان‌تر</t>
+          <t>⚪ بدون تطابق</t>
         </is>
       </c>
     </row>
@@ -4229,23 +2475,27 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Mashrooms and Veggie Cigar میکس سه نوع قارچ سس ورچستر t</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="n">
-        <v>598000</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G51" s="3" t="n">
-        <v>-209700</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>🟢 ارزان‌تر</t>
+          <t>⚪ بدون تطابق</t>
         </is>
       </c>
     </row>
@@ -4385,23 +2635,27 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Korean Fried Chicken مرغ سوخاری سس چیلی کُره ای و خیارشور t</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="n">
-        <v>693000</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G55" s="3" t="n">
-        <v>93500</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>🔴 گران‌تر</t>
+          <t>⚪ بدون تطابق</t>
         </is>
       </c>
     </row>
@@ -4461,23 +2715,27 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Nakaya Panko Steak استیک تندرلوین سوخاری شده سس قارچ خامه ای سالاد کرانچی t</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="n">
-        <v>166500</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G57" s="3" t="n">
-        <v>983000</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>🔴 گران‌تر</t>
+          <t>⚪ بدون تطابق</t>
         </is>
       </c>
     </row>
@@ -4617,23 +2875,27 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Classic Mojito کلاسیک موهیتو t Classic Mojito t</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="n">
-        <v>356000</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G61" s="3" t="n">
-        <v>436000</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>🔴 گران‌تر</t>
+          <t>⚪ بدون تطابق</t>
         </is>
       </c>
     </row>
@@ -4653,23 +2915,27 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Korean Fried Chicken مرغ سوخاری سس چیلی کُره ای و خیارشور t</t>
-        </is>
-      </c>
-      <c r="E62" s="4" t="n">
-        <v>693000</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G62" s="4" t="n">
-        <v>287100</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>🔴 گران‌تر</t>
+          <t>⚪ بدون تطابق</t>
         </is>
       </c>
     </row>
@@ -4689,23 +2955,27 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>Pad Thai Noodles chicken چیکن نودل برنج تخم مرغ میکس سبزیجات سس ترش و شیرین t</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="n">
-        <v>151200</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G63" s="3" t="n">
-        <v>732100</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>🔴 گران‌تر</t>
+          <t>⚪ بدون تطابق</t>
         </is>
       </c>
     </row>
@@ -4725,23 +2995,27 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Korean Fried Chicken مرغ سوخاری سس چیلی کُره ای و خیارشور t</t>
-        </is>
-      </c>
-      <c r="E64" s="4" t="n">
-        <v>693000</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G64" s="4" t="n">
-        <v>-341000</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>🟢 ارزان‌تر</t>
+          <t>⚪ بدون تطابق</t>
         </is>
       </c>
     </row>
@@ -4761,23 +3035,27 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Korean Fried Chicken مرغ سوخاری سس چیلی کُره ای و خیارشور t</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="n">
-        <v>693000</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G65" s="3" t="n">
-        <v>-363000</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>🟢 ارزان‌تر</t>
+          <t>⚪ بدون تطابق</t>
         </is>
       </c>
     </row>
@@ -4797,23 +3075,27 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Vegetable Noodles نودل میکس سبزیجات سس سیشوان t</t>
-        </is>
-      </c>
-      <c r="E66" s="4" t="n">
-        <v>107000</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G66" s="4" t="n">
-        <v>188900</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>🔴 گران‌تر</t>
+          <t>⚪ بدون تطابق</t>
         </is>
       </c>
     </row>
@@ -4913,23 +3195,27 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>Korean Fried Chicken مرغ سوخاری سس چیلی کُره ای و خیارشور t</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="n">
-        <v>693000</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G69" s="3" t="n">
-        <v>-577500</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>🟢 ارزان‌تر</t>
+          <t>⚪ بدون تطابق</t>
         </is>
       </c>
     </row>
@@ -4949,23 +3235,27 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Steam Rice برنج بخارپز t Steam Rice t</t>
-        </is>
-      </c>
-      <c r="E70" s="4" t="n">
-        <v>315000</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G70" s="4" t="n">
-        <v>-145600</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>🟢 ارزان‌تر</t>
+          <t>⚪ بدون تطابق</t>
         </is>
       </c>
     </row>
@@ -4985,23 +3275,27 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Chicken Teryaki مرغ گریل شده در سس تریاکی برنج بخارپز سبزیجات گریل شده t</t>
-        </is>
-      </c>
-      <c r="E71" s="3" t="n">
-        <v>107000</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G71" s="3" t="n">
-        <v>183400</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>🔴 گران‌تر</t>
+          <t>⚪ بدون تطابق</t>
         </is>
       </c>
     </row>
@@ -5021,23 +3315,27 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Vegetable Noodles نودل میکس سبزیجات سس سیشوان t</t>
-        </is>
-      </c>
-      <c r="E72" s="4" t="n">
-        <v>107000</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G72" s="4" t="n">
-        <v>449600</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>🔴 گران‌تر</t>
+          <t>⚪ بدون تطابق</t>
         </is>
       </c>
     </row>
@@ -5097,23 +3395,27 @@
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Rock &amp; Roll سوریمی خیار مامی نوری میگو راک t</t>
-        </is>
-      </c>
-      <c r="E74" s="4" t="n">
-        <v>235700</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G74" s="4" t="n">
-        <v>411100</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>🔴 گران‌تر</t>
+          <t>⚪ بدون تطابق</t>
         </is>
       </c>
     </row>
@@ -5133,23 +3435,27 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>Chicken Teryaki مرغ گریل شده در سس تریاکی برنج بخارپز سبزیجات گریل شده t</t>
-        </is>
-      </c>
-      <c r="E75" s="3" t="n">
-        <v>107000</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G75" s="3" t="n">
-        <v>721300</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>🔴 گران‌تر</t>
+          <t>⚪ بدون تطابق</t>
         </is>
       </c>
     </row>
@@ -5169,23 +3475,27 @@
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Korean Fried Chicken مرغ سوخاری سس چیلی کُره ای و خیارشور t</t>
-        </is>
-      </c>
-      <c r="E76" s="4" t="n">
-        <v>693000</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G76" s="4" t="n">
-        <v>20900</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>🔴 گران‌تر</t>
+          <t>⚪ بدون تطابق</t>
         </is>
       </c>
     </row>
@@ -5245,23 +3555,27 @@
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Vegetable Noodles نودل میکس سبزیجات سس سیشوان t</t>
-        </is>
-      </c>
-      <c r="E78" s="4" t="n">
-        <v>107000</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G78" s="4" t="n">
-        <v>648700</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>🔴 گران‌تر</t>
+          <t>⚪ بدون تطابق</t>
         </is>
       </c>
     </row>
@@ -5281,23 +3595,27 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>Chicken Teryaki مرغ گریل شده در سس تریاکی برنج بخارپز سبزیجات گریل شده t</t>
-        </is>
-      </c>
-      <c r="E79" s="3" t="n">
-        <v>107000</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G79" s="3" t="n">
-        <v>449600</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H79" s="3" t="inlineStr">
         <is>
-          <t>🔴 گران‌تر</t>
+          <t>⚪ بدون تطابق</t>
         </is>
       </c>
     </row>
@@ -5357,23 +3675,27 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>Beef Noodles بیف به همراه فلفل سیاه فلفل رنگی پیازچه t</t>
-        </is>
-      </c>
-      <c r="E81" s="3" t="n">
-        <v>171200</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G81" s="3" t="n">
-        <v>1038800</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H81" s="3" t="inlineStr">
         <is>
-          <t>🔴 گران‌تر</t>
+          <t>⚪ بدون تطابق</t>
         </is>
       </c>
     </row>
@@ -5433,23 +3755,27 @@
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>Nakaya Panko Steak استیک تندرلوین سوخاری شده سس قارچ خامه ای سالاد کرانچی t</t>
-        </is>
-      </c>
-      <c r="E83" s="3" t="n">
-        <v>166500</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G83" s="3" t="n">
-        <v>946700</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>🔴 گران‌تر</t>
+          <t>⚪ بدون تطابق</t>
         </is>
       </c>
     </row>
@@ -5549,23 +3875,27 @@
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Korean Fried Chicken مرغ سوخاری سس چیلی کُره ای و خیارشور t</t>
-        </is>
-      </c>
-      <c r="E86" s="4" t="n">
-        <v>693000</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G86" s="4" t="n">
-        <v>-114400</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>🟢 ارزان‌تر</t>
+          <t>⚪ بدون تطابق</t>
         </is>
       </c>
     </row>
@@ -5705,23 +4035,27 @@
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Lemonade لیموناد t Lemonade t</t>
-        </is>
-      </c>
-      <c r="E90" s="4" t="n">
-        <v>316000</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G90" s="4" t="n">
-        <v>-246000</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>🟢 ارزان‌تر</t>
+          <t>⚪ بدون تطابق</t>
         </is>
       </c>
     </row>
@@ -5741,23 +4075,27 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>Classic Mojito کلاسیک موهیتو t Classic Mojito t</t>
-        </is>
-      </c>
-      <c r="E91" s="3" t="n">
-        <v>356000</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G91" s="3" t="n">
-        <v>-276000</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H91" s="3" t="inlineStr">
         <is>
-          <t>🟢 ارزان‌تر</t>
+          <t>⚪ بدون تطابق</t>
         </is>
       </c>
     </row>
@@ -5817,23 +4155,27 @@
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>Korean Fried Chicken مرغ سوخاری سس چیلی کُره ای و خیارشور t</t>
-        </is>
-      </c>
-      <c r="E93" s="3" t="n">
-        <v>693000</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G93" s="3" t="n">
-        <v>-550000</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H93" s="3" t="inlineStr">
         <is>
-          <t>🟢 ارزان‌تر</t>
+          <t>⚪ بدون تطابق</t>
         </is>
       </c>
     </row>
@@ -5893,23 +4235,27 @@
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>Crispy Maki Roll میگو کاتسو آووکادو خیار مایونز ژاپنی t</t>
-        </is>
-      </c>
-      <c r="E95" s="3" t="n">
-        <v>125900</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>ناکایا</t>
-        </is>
-      </c>
-      <c r="G95" s="3" t="n">
-        <v>50100</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H95" s="3" t="inlineStr">
         <is>
-          <t>🔴 گران‌تر</t>
+          <t>⚪ بدون تطابق</t>
         </is>
       </c>
     </row>
@@ -5921,7 +4267,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5941,7 +4287,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>📊 مقایسه منو — برگر فکتوری  |  تعداد رقبا: 6</t>
         </is>
@@ -8837,7 +7183,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8857,7 +7203,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>📊 مقایسه منو — لفو  |  تعداد رقبا: 4</t>
         </is>

--- a/reports/MenuRadar_2026-06-08.xlsx
+++ b/reports/MenuRadar_2026-06-08.xlsx
@@ -7,9 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="روماتای" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="برگر فکتوری" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="لفو" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="خلاصه کل" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="روماتای" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="برگر فکتوری" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="لفو" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,6 +43,12 @@
     <font>
       <name val="Arial"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
     </font>
   </fonts>
   <fills count="6">
@@ -98,9 +105,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -111,6 +118,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,6 +487,1846 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>📋 خلاصه مقایسه قیمت — همه کانسپت‌ها</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>کانسپت</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>آیتم من</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>قیمت من (تومان)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>آیتم رقیب</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>قیمت رقیب (تومان)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>رقیب</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>اختلاف (تومان)</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>وضعیت</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>روماتای</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>پانینی اسفناج</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>258500</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>BOP باپ t BOP برنج داغ به همراه سس مخصوص باپ اسفناج پنیر پارمیزان t</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>145500</v>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>113000</v>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>🔴 گران‌تر</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>روماتای</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>نودل سوپ مرغ</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>786500</v>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Pad Thai Noodles chicken چیکن نودل برنج تخم مرغ میکس سبزیجات سس ترش و شیرین t</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>151200</v>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>635300</v>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>🔴 گران‌تر</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>روماتای</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>نان سیر</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>435600</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Asian Chopped Chicken مرغ گریل شده کلم سفید کلم قرمز گشنیز نان کریسپی سس کنجد t</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>904000</v>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>-468400</v>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>🟢 ارزان‌تر</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>روماتای</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>نودل سرخ شده با مرغ سبزیجات</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>871200</v>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Chicken Noodles مرغ مزه دار شده میکس سبزیجات سس سیشوان t</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>124500</v>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>746700</v>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>🔴 گران‌تر</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>روماتای</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>نودل سرخ شده با میگوسبزیجات</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>1452000</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Nakaya Maki میگو سرخ شده سوریمی کاتسو آووکادو توبیکو سبز سلمن t</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>214300</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>1237700</v>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>🔴 گران‌تر</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>روماتای</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">برنج سرخ شده با مرغ سبزیجات </t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>665500</v>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Chicken Teryaki مرغ گریل شده در سس تریاکی برنج بخارپز سبزیجات گریل شده t</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>107000</v>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>558500</v>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>🔴 گران‌تر</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>روماتای</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>برنج سرخ شده با گوشت سبزیجات</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>1089000</v>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Beef Teryaki گوشت گریل شده در سس تریاکی برنج بخارپز سبزیجات گریل شده t</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>206000</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>883000</v>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>🔴 گران‌تر</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>روماتای</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>برنج سرخ شده با میگو سبزیجات</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>1306800</v>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Shrimp Teryaki میگو گریل شده در سس تریاکی برنج بخارپز سبزیجات گریل شده t</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>278000</v>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>1028800</v>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>🔴 گران‌تر</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>روماتای</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>بیف تریاكی</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>1089000</v>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Beef Noodles بیف به همراه فلفل سیاه فلفل رنگی پیازچه t</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>171200</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>917800</v>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>🔴 گران‌تر</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>روماتای</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>مرغ کانتون</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>711700</v>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Korean Fried Chicken مرغ سوخاری سس چیلی کُره ای و خیارشور t</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>693000</v>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>18700</v>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>🔴 گران‌تر</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>روماتای</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>میگو سوخاری</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>1210000</v>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Crispy Maki Roll میگو کاتسو آووکادو خیار مایونز ژاپنی t</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>125900</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>1084100</v>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>🔴 گران‌تر</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>روماتای</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> پاستا سبزیجات</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>653400</v>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Vegetable Noodles نودل میکس سبزیجات سس سیشوان t</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>107000</v>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>546400</v>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>🔴 گران‌تر</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>روماتای</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>سیب زمینی سرخ شده روماتای</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>255200</v>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Nakaya Maki میگو سرخ شده سوریمی کاتسو آووکادو توبیکو سبز سلمن t</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>214300</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>40900</v>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>🔴 گران‌تر</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>روماتای</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>برنج بخارپز</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>254100</v>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Steam Rice برنج بخارپز t Steam Rice t</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>315000</v>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>-60900</v>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>🟢 ارزان‌تر</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>روماتای</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>بیف استراگانف</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>1149500</v>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Beef Noodles بیف به همراه فلفل سیاه فلفل رنگی پیازچه t</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>171200</v>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>978300</v>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>🔴 گران‌تر</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>روماتای</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>فیله مرغ</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>181500</v>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Korean Fried Chicken مرغ سوخاری سس چیلی کُره ای و خیارشور t</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>693000</v>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>-511500</v>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>🟢 ارزان‌تر</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>روماتای</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>روکولا</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>133100</v>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Beef Sliders بیف قارچ واسابی خامه ای چدار روکولا سس هالوپینو t</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>627000</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>-493900</v>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>🟢 ارزان‌تر</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>روماتای</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>قارچ روماتای</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>271700</v>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Miso Mashroom توفو جلبک دریایی پیازچه مخلوط قارچ t</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>482000</v>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>-210300</v>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>🟢 ارزان‌تر</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>روماتای</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>پنیر پیتزا</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>41000</v>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Crazy Mushroom Maki قارچ تمپپرا پنیر آووکادو خیار سس پونزو t</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>156900</v>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>-115900</v>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>🟢 ارزان‌تر</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>روماتای</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>چیكن ماشروم</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>750200</v>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Miso Mashroom میسو ماشروم t Miso Mashroom توفو جلبک دریایی پیازچه مخلوط قارچ t</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>482000</v>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>268200</v>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>🔴 گران‌تر</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>روماتای</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>شنیسل مرغ با سس قارچ</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>750200</v>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Tamari Fried Ch مرغ میکس سبزیجات تخم مرغ قارچ سس تاماری t</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>796000</v>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>-45800</v>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>🟢 ارزان‌تر</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>روماتای</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>چیکن استراگانف</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>695200</v>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Korean Fried Chicken مرغ سوخاری سس چیلی کُره ای و خیارشور t</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>693000</v>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>2200</v>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>🟡 مشابه</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>روماتای</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>میکس برنج و نودل سرخ شده</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>592900</v>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Pad Thai Noodles chicken چیکن نودل برنج تخم مرغ میکس سبزیجات سس ترش و شیرین t</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>151200</v>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>441700</v>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>🔴 گران‌تر</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>روماتای</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>سس سبز</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>49500</v>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Salmon oshi sushi سلمن آووکادو سس چیلی گارلیک فلفل سبز t</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>206800</v>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>-157300</v>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>🟢 ارزان‌تر</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>روماتای</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>سیب زمینی با سس قارچ روماتای</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>388300</v>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Mashrooms and Veggie Cigar میکس سه نوع قارچ سس ورچستر t</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>598000</v>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>-209700</v>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>🟢 ارزان‌تر</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>روماتای</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>چیکن فونگی</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>786500</v>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Korean Fried Chicken مرغ سوخاری سس چیلی کُره ای و خیارشور t</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>693000</v>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>93500</v>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>🔴 گران‌تر</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>روماتای</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیتزا استیک </t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>1149500</v>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Nakaya Panko Steak استیک تندرلوین سوخاری شده سس قارچ خامه ای سالاد کرانچی t</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>166500</v>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>983000</v>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>🔴 گران‌تر</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>روماتای</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>لازانیا کلاسیک</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>792000</v>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Classic Mojito کلاسیک موهیتو t Classic Mojito t</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>356000</v>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>436000</v>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>🔴 گران‌تر</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>روماتای</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>چیکن فلورنتینو</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>980100</v>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Korean Fried Chicken مرغ سوخاری سس چیلی کُره ای و خیارشور t</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>693000</v>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>287100</v>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>🔴 گران‌تر</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>روماتای</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>مرغ ترش و شیرین</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>883300</v>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Pad Thai Noodles chicken چیکن نودل برنج تخم مرغ میکس سبزیجات سس ترش و شیرین t</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>151200</v>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>732100</v>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>🔴 گران‌تر</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>روماتای</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">بال مرغ </t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>352000</v>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Korean Fried Chicken مرغ سوخاری سس چیلی کُره ای و خیارشور t</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>693000</v>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>-341000</v>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>🟢 ارزان‌تر</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>روماتای</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>رول مرغ و قارچ</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>330000</v>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>Korean Fried Chicken مرغ سوخاری سس چیلی کُره ای و خیارشور t</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>693000</v>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>-363000</v>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>🟢 ارزان‌تر</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>روماتای</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>رول سبزیجات</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>295900</v>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Vegetable Noodles نودل میکس سبزیجات سس سیشوان t</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>107000</v>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>188900</v>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>🔴 گران‌تر</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>روماتای</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>رول مرغ و قارچ عددی</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>115500</v>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>Korean Fried Chicken مرغ سوخاری سس چیلی کُره ای و خیارشور t</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>693000</v>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>-577500</v>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>🟢 ارزان‌تر</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>روماتای</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>برنج بخارپز ساید</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>169400</v>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Steam Rice برنج بخارپز t Steam Rice t</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>315000</v>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>-145600</v>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>🟢 ارزان‌تر</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>روماتای</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>برنج سرخ شده سبزیجات ساید</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>290400</v>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>Chicken Teryaki مرغ گریل شده در سس تریاکی برنج بخارپز سبزیجات گریل شده t</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>107000</v>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>183400</v>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>🔴 گران‌تر</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>روماتای</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>نودل سرخ شده سبزیجات ساید</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>556600</v>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Vegetable Noodles نودل میکس سبزیجات سس سیشوان t</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>107000</v>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>449600</v>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>🔴 گران‌تر</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>روماتای</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>راک شریمپ</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>646800</v>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>Rock &amp; Roll سوریمی خیار مامی نوری میگو راک t</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>235700</v>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>411100</v>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>🔴 گران‌تر</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>روماتای</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>تریاکی چیکن</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>828300</v>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Chicken Teryaki مرغ گریل شده در سس تریاکی برنج بخارپز سبزیجات گریل شده t</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>107000</v>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>721300</v>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>🔴 گران‌تر</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>روماتای</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>چیکن سامبال</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>713900</v>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>Korean Fried Chicken مرغ سوخاری سس چیلی کُره ای و خیارشور t</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>693000</v>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>20900</v>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>🔴 گران‌تر</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>روماتای</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>نودل با سبزیجات</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>755700</v>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Vegetable Noodles نودل میکس سبزیجات سس سیشوان t</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>107000</v>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>648700</v>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>🔴 گران‌تر</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>روماتای</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>برنج با سبزیجات</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="n">
+        <v>556600</v>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>Chicken Teryaki مرغ گریل شده در سس تریاکی برنج بخارپز سبزیجات گریل شده t</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>107000</v>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>449600</v>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>🔴 گران‌تر</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>روماتای</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>بیف بیزیل</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>1210000</v>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Beef Noodles بیف به همراه فلفل سیاه فلفل رنگی پیازچه t</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>171200</v>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>1038800</v>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>🔴 گران‌تر</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>روماتای</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>استیک پراوانس</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>1113200</v>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>Nakaya Panko Steak استیک تندرلوین سوخاری شده سس قارچ خامه ای سالاد کرانچی t</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>166500</v>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>946700</v>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>🔴 گران‌تر</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>روماتای</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>کالزونه مرغ و اسفناج</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>578600</v>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Korean Fried Chicken مرغ سوخاری سس چیلی کُره ای و خیارشور t</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>693000</v>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>-114400</v>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>🟢 ارزان‌تر</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>روماتای</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>لیموناد قوطی</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="n">
+        <v>70000</v>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>Lemonade لیموناد t Lemonade t</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>316000</v>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>-246000</v>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>🟢 ارزان‌تر</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>روماتای</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>موهیتو قوطی</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>80000</v>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Classic Mojito کلاسیک موهیتو t Classic Mojito t</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>356000</v>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>-276000</v>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>🟢 ارزان‌تر</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>روماتای</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>فیله مرغ سوخاری عددی</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>143000</v>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>Korean Fried Chicken مرغ سوخاری سس چیلی کُره ای و خیارشور t</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>693000</v>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>-550000</v>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>🟢 ارزان‌تر</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>روماتای</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>میگو سوخاری عددی</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>176000</v>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Crispy Maki Roll میگو کاتسو آووکادو خیار مایونز ژاپنی t</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>125900</v>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>50100</v>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>🔴 گران‌تر</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -491,7 +2341,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>📊 مقایسه منو — روماتای  |  تعداد رقبا: 9</t>
         </is>
@@ -555,27 +2405,23 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>BOP باپ t BOP برنج داغ به همراه سس مخصوص باپ اسفناج پنیر پارمیزان t</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>145500</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>113000</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>⚪ بدون تطابق</t>
+          <t>🔴 گران‌تر</t>
         </is>
       </c>
     </row>
@@ -675,27 +2521,23 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Pad Thai Noodles chicken چیکن نودل برنج تخم مرغ میکس سبزیجات سس ترش و شیرین t</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>151200</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>635300</v>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>⚪ بدون تطابق</t>
+          <t>🔴 گران‌تر</t>
         </is>
       </c>
     </row>
@@ -755,27 +2597,23 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Asian Chopped Chicken مرغ گریل شده کلم سفید کلم قرمز گشنیز نان کریسپی سس کنجد t</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>904000</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>-468400</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>⚪ بدون تطابق</t>
+          <t>🟢 ارزان‌تر</t>
         </is>
       </c>
     </row>
@@ -875,27 +2713,23 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Chicken Noodles مرغ مزه دار شده میکس سبزیجات سس سیشوان t</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>124500</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>746700</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>⚪ بدون تطابق</t>
+          <t>🔴 گران‌تر</t>
         </is>
       </c>
     </row>
@@ -955,27 +2789,23 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Nakaya Maki میگو سرخ شده سوریمی کاتسو آووکادو توبیکو سبز سلمن t</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>214300</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>1237700</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>⚪ بدون تطابق</t>
+          <t>🔴 گران‌تر</t>
         </is>
       </c>
     </row>
@@ -995,27 +2825,23 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Chicken Teryaki مرغ گریل شده در سس تریاکی برنج بخارپز سبزیجات گریل شده t</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>107000</v>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>558500</v>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>⚪ بدون تطابق</t>
+          <t>🔴 گران‌تر</t>
         </is>
       </c>
     </row>
@@ -1035,27 +2861,23 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Beef Teryaki گوشت گریل شده در سس تریاکی برنج بخارپز سبزیجات گریل شده t</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>206000</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>883000</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>⚪ بدون تطابق</t>
+          <t>🔴 گران‌تر</t>
         </is>
       </c>
     </row>
@@ -1075,27 +2897,23 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Shrimp Teryaki میگو گریل شده در سس تریاکی برنج بخارپز سبزیجات گریل شده t</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>278000</v>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>1028800</v>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>⚪ بدون تطابق</t>
+          <t>🔴 گران‌تر</t>
         </is>
       </c>
     </row>
@@ -1115,27 +2933,23 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Beef Noodles بیف به همراه فلفل سیاه فلفل رنگی پیازچه t</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>171200</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>917800</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>⚪ بدون تطابق</t>
+          <t>🔴 گران‌تر</t>
         </is>
       </c>
     </row>
@@ -1195,27 +3009,23 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Korean Fried Chicken مرغ سوخاری سس چیلی کُره ای و خیارشور t</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>693000</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>18700</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>⚪ بدون تطابق</t>
+          <t>🔴 گران‌تر</t>
         </is>
       </c>
     </row>
@@ -1235,27 +3045,23 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Crispy Maki Roll میگو کاتسو آووکادو خیار مایونز ژاپنی t</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>125900</v>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>1084100</v>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>⚪ بدون تطابق</t>
+          <t>🔴 گران‌تر</t>
         </is>
       </c>
     </row>
@@ -1275,27 +3081,23 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Vegetable Noodles نودل میکس سبزیجات سس سیشوان t</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>107000</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>546400</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>⚪ بدون تطابق</t>
+          <t>🔴 گران‌تر</t>
         </is>
       </c>
     </row>
@@ -1675,27 +3477,23 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Nakaya Maki میگو سرخ شده سوریمی کاتسو آووکادو توبیکو سبز سلمن t</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>214300</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>40900</v>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>⚪ بدون تطابق</t>
+          <t>🔴 گران‌تر</t>
         </is>
       </c>
     </row>
@@ -1715,27 +3513,23 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Steam Rice برنج بخارپز t Steam Rice t</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>315000</v>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>-60900</v>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>⚪ بدون تطابق</t>
+          <t>🟢 ارزان‌تر</t>
         </is>
       </c>
     </row>
@@ -1755,27 +3549,23 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Beef Noodles بیف به همراه فلفل سیاه فلفل رنگی پیازچه t</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>171200</v>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>978300</v>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>⚪ بدون تطابق</t>
+          <t>🔴 گران‌تر</t>
         </is>
       </c>
     </row>
@@ -1835,27 +3625,23 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Korean Fried Chicken مرغ سوخاری سس چیلی کُره ای و خیارشور t</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>693000</v>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>-511500</v>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>⚪ بدون تطابق</t>
+          <t>🟢 ارزان‌تر</t>
         </is>
       </c>
     </row>
@@ -1875,27 +3661,23 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Beef Sliders بیف قارچ واسابی خامه ای چدار روکولا سس هالوپینو t</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>627000</v>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G36" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>-493900</v>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>⚪ بدون تطابق</t>
+          <t>🟢 ارزان‌تر</t>
         </is>
       </c>
     </row>
@@ -1915,27 +3697,23 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Miso Mashroom توفو جلبک دریایی پیازچه مخلوط قارچ t</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>482000</v>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>-210300</v>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>⚪ بدون تطابق</t>
+          <t>🟢 ارزان‌تر</t>
         </is>
       </c>
     </row>
@@ -1995,27 +3773,23 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Crazy Mushroom Maki قارچ تمپپرا پنیر آووکادو خیار سس پونزو t</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>156900</v>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>-115900</v>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>⚪ بدون تطابق</t>
+          <t>🟢 ارزان‌تر</t>
         </is>
       </c>
     </row>
@@ -2075,27 +3849,23 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Miso Mashroom میسو ماشروم t Miso Mashroom توفو جلبک دریایی پیازچه مخلوط قارچ t</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>482000</v>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>268200</v>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>⚪ بدون تطابق</t>
+          <t>🔴 گران‌تر</t>
         </is>
       </c>
     </row>
@@ -2115,27 +3885,23 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Tamari Fried Ch مرغ میکس سبزیجات تخم مرغ قارچ سس تاماری t</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>796000</v>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G42" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>-45800</v>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>⚪ بدون تطابق</t>
+          <t>🟢 ارزان‌تر</t>
         </is>
       </c>
     </row>
@@ -2235,27 +4001,23 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Korean Fried Chicken مرغ سوخاری سس چیلی کُره ای و خیارشور t</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>693000</v>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>2200</v>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>⚪ بدون تطابق</t>
+          <t>🟡 مشابه</t>
         </is>
       </c>
     </row>
@@ -2315,27 +4077,23 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Pad Thai Noodles chicken چیکن نودل برنج تخم مرغ میکس سبزیجات سس ترش و شیرین t</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>151200</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>441700</v>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>⚪ بدون تطابق</t>
+          <t>🔴 گران‌تر</t>
         </is>
       </c>
     </row>
@@ -2395,27 +4153,23 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Salmon oshi sushi سلمن آووکادو سس چیلی گارلیک فلفل سبز t</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>206800</v>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G49" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>-157300</v>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>⚪ بدون تطابق</t>
+          <t>🟢 ارزان‌تر</t>
         </is>
       </c>
     </row>
@@ -2475,27 +4229,23 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Mashrooms and Veggie Cigar میکس سه نوع قارچ سس ورچستر t</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>598000</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G51" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>-209700</v>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>⚪ بدون تطابق</t>
+          <t>🟢 ارزان‌تر</t>
         </is>
       </c>
     </row>
@@ -2635,27 +4385,23 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Korean Fried Chicken مرغ سوخاری سس چیلی کُره ای و خیارشور t</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>693000</v>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G55" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>93500</v>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>⚪ بدون تطابق</t>
+          <t>🔴 گران‌تر</t>
         </is>
       </c>
     </row>
@@ -2715,27 +4461,23 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Nakaya Panko Steak استیک تندرلوین سوخاری شده سس قارچ خامه ای سالاد کرانچی t</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>166500</v>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G57" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>983000</v>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>⚪ بدون تطابق</t>
+          <t>🔴 گران‌تر</t>
         </is>
       </c>
     </row>
@@ -2875,27 +4617,23 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Classic Mojito کلاسیک موهیتو t Classic Mojito t</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>356000</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G61" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>436000</v>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>⚪ بدون تطابق</t>
+          <t>🔴 گران‌تر</t>
         </is>
       </c>
     </row>
@@ -2915,27 +4653,23 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Korean Fried Chicken مرغ سوخاری سس چیلی کُره ای و خیارشور t</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="n">
+        <v>693000</v>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G62" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="n">
+        <v>287100</v>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>⚪ بدون تطابق</t>
+          <t>🔴 گران‌تر</t>
         </is>
       </c>
     </row>
@@ -2955,27 +4689,23 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Pad Thai Noodles chicken چیکن نودل برنج تخم مرغ میکس سبزیجات سس ترش و شیرین t</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>151200</v>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G63" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>732100</v>
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>⚪ بدون تطابق</t>
+          <t>🔴 گران‌تر</t>
         </is>
       </c>
     </row>
@@ -2995,27 +4725,23 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Korean Fried Chicken مرغ سوخاری سس چیلی کُره ای و خیارشور t</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="n">
+        <v>693000</v>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G64" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="n">
+        <v>-341000</v>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>⚪ بدون تطابق</t>
+          <t>🟢 ارزان‌تر</t>
         </is>
       </c>
     </row>
@@ -3035,27 +4761,23 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Korean Fried Chicken مرغ سوخاری سس چیلی کُره ای و خیارشور t</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>693000</v>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G65" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="n">
+        <v>-363000</v>
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>⚪ بدون تطابق</t>
+          <t>🟢 ارزان‌تر</t>
         </is>
       </c>
     </row>
@@ -3075,27 +4797,23 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Vegetable Noodles نودل میکس سبزیجات سس سیشوان t</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="n">
+        <v>107000</v>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G66" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="n">
+        <v>188900</v>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>⚪ بدون تطابق</t>
+          <t>🔴 گران‌تر</t>
         </is>
       </c>
     </row>
@@ -3195,27 +4913,23 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Korean Fried Chicken مرغ سوخاری سس چیلی کُره ای و خیارشور t</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>693000</v>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G69" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>-577500</v>
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>⚪ بدون تطابق</t>
+          <t>🟢 ارزان‌تر</t>
         </is>
       </c>
     </row>
@@ -3235,27 +4949,23 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Steam Rice برنج بخارپز t Steam Rice t</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="n">
+        <v>315000</v>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="n">
+        <v>-145600</v>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>⚪ بدون تطابق</t>
+          <t>🟢 ارزان‌تر</t>
         </is>
       </c>
     </row>
@@ -3275,27 +4985,23 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Chicken Teryaki مرغ گریل شده در سس تریاکی برنج بخارپز سبزیجات گریل شده t</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>107000</v>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="n">
+        <v>183400</v>
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>⚪ بدون تطابق</t>
+          <t>🔴 گران‌تر</t>
         </is>
       </c>
     </row>
@@ -3315,27 +5021,23 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Vegetable Noodles نودل میکس سبزیجات سس سیشوان t</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="n">
+        <v>107000</v>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G72" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="n">
+        <v>449600</v>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>⚪ بدون تطابق</t>
+          <t>🔴 گران‌تر</t>
         </is>
       </c>
     </row>
@@ -3395,27 +5097,23 @@
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Rock &amp; Roll سوریمی خیار مامی نوری میگو راک t</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="n">
+        <v>235700</v>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="n">
+        <v>411100</v>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>⚪ بدون تطابق</t>
+          <t>🔴 گران‌تر</t>
         </is>
       </c>
     </row>
@@ -3435,27 +5133,23 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E75" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Chicken Teryaki مرغ گریل شده در سس تریاکی برنج بخارپز سبزیجات گریل شده t</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>107000</v>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G75" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>721300</v>
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>⚪ بدون تطابق</t>
+          <t>🔴 گران‌تر</t>
         </is>
       </c>
     </row>
@@ -3475,27 +5169,23 @@
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Korean Fried Chicken مرغ سوخاری سس چیلی کُره ای و خیارشور t</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="n">
+        <v>693000</v>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G76" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="n">
+        <v>20900</v>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>⚪ بدون تطابق</t>
+          <t>🔴 گران‌تر</t>
         </is>
       </c>
     </row>
@@ -3555,27 +5245,23 @@
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Vegetable Noodles نودل میکس سبزیجات سس سیشوان t</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="n">
+        <v>107000</v>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="n">
+        <v>648700</v>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>⚪ بدون تطابق</t>
+          <t>🔴 گران‌تر</t>
         </is>
       </c>
     </row>
@@ -3595,27 +5281,23 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Chicken Teryaki مرغ گریل شده در سس تریاکی برنج بخارپز سبزیجات گریل شده t</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>107000</v>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>449600</v>
       </c>
       <c r="H79" s="3" t="inlineStr">
         <is>
-          <t>⚪ بدون تطابق</t>
+          <t>🔴 گران‌تر</t>
         </is>
       </c>
     </row>
@@ -3675,27 +5357,23 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Beef Noodles بیف به همراه فلفل سیاه فلفل رنگی پیازچه t</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>171200</v>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>1038800</v>
       </c>
       <c r="H81" s="3" t="inlineStr">
         <is>
-          <t>⚪ بدون تطابق</t>
+          <t>🔴 گران‌تر</t>
         </is>
       </c>
     </row>
@@ -3755,27 +5433,23 @@
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E83" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Nakaya Panko Steak استیک تندرلوین سوخاری شده سس قارچ خامه ای سالاد کرانچی t</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>166500</v>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G83" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>946700</v>
       </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>⚪ بدون تطابق</t>
+          <t>🔴 گران‌تر</t>
         </is>
       </c>
     </row>
@@ -3875,27 +5549,23 @@
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E86" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Korean Fried Chicken مرغ سوخاری سس چیلی کُره ای و خیارشور t</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="n">
+        <v>693000</v>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G86" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="n">
+        <v>-114400</v>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>⚪ بدون تطابق</t>
+          <t>🟢 ارزان‌تر</t>
         </is>
       </c>
     </row>
@@ -4035,27 +5705,23 @@
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E90" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Lemonade لیموناد t Lemonade t</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="n">
+        <v>316000</v>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G90" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="n">
+        <v>-246000</v>
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>⚪ بدون تطابق</t>
+          <t>🟢 ارزان‌تر</t>
         </is>
       </c>
     </row>
@@ -4075,27 +5741,23 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E91" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Classic Mojito کلاسیک موهیتو t Classic Mojito t</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>356000</v>
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G91" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="n">
+        <v>-276000</v>
       </c>
       <c r="H91" s="3" t="inlineStr">
         <is>
-          <t>⚪ بدون تطابق</t>
+          <t>🟢 ارزان‌تر</t>
         </is>
       </c>
     </row>
@@ -4155,27 +5817,23 @@
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E93" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Korean Fried Chicken مرغ سوخاری سس چیلی کُره ای و خیارشور t</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>693000</v>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G93" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="n">
+        <v>-550000</v>
       </c>
       <c r="H93" s="3" t="inlineStr">
         <is>
-          <t>⚪ بدون تطابق</t>
+          <t>🟢 ارزان‌تر</t>
         </is>
       </c>
     </row>
@@ -4235,27 +5893,23 @@
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E95" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Crispy Maki Roll میگو کاتسو آووکادو خیار مایونز ژاپنی t</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>125900</v>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G95" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ناکایا</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="n">
+        <v>50100</v>
       </c>
       <c r="H95" s="3" t="inlineStr">
         <is>
-          <t>⚪ بدون تطابق</t>
+          <t>🔴 گران‌تر</t>
         </is>
       </c>
     </row>
@@ -4267,7 +5921,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4287,7 +5941,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>📊 مقایسه منو — برگر فکتوری  |  تعداد رقبا: 6</t>
         </is>
@@ -7183,7 +8837,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7203,7 +8857,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>📊 مقایسه منو — لفو  |  تعداد رقبا: 4</t>
         </is>
